--- a/output/yearly_benthic_cover_iteration_13_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_13_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.42830515756423</v>
+        <v>45.04499765763666</v>
       </c>
       <c r="M2" t="n">
-        <v>99.61099836016626</v>
+        <v>100.1549536108869</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.98617817977373</v>
+        <v>88.06922421807596</v>
       </c>
       <c r="C3" t="n">
-        <v>45.86756982422168</v>
+        <v>45.93142542198285</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228671430594385</v>
+        <v>2.22883601348164</v>
       </c>
       <c r="E3" t="n">
-        <v>5.669356401318533</v>
+        <v>5.710267582572784</v>
       </c>
       <c r="F3" t="n">
-        <v>0.742890476864795</v>
+        <v>0.7429453378272133</v>
       </c>
       <c r="G3" t="n">
-        <v>33.95230771540395</v>
+        <v>33.97362403739398</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17296193578057</v>
+        <v>34.17548554005181</v>
       </c>
       <c r="I3" t="n">
-        <v>6.576924739406532</v>
+        <v>6.59465734532845</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643065480404969</v>
+        <v>4.643408361420082</v>
       </c>
       <c r="K3" t="n">
-        <v>12.01382182022627</v>
+        <v>11.93077578192404</v>
       </c>
       <c r="L3" t="n">
-        <v>48.88252421505037</v>
+        <v>48.90109560912236</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7639158594983</v>
+        <v>106.7632968130293</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.08600673193831</v>
+        <v>87.27991929650229</v>
       </c>
       <c r="C4" t="n">
-        <v>42.60651634570827</v>
+        <v>42.78229268099756</v>
       </c>
       <c r="D4" t="n">
-        <v>2.185318711967104</v>
+        <v>2.191461823908504</v>
       </c>
       <c r="E4" t="n">
-        <v>6.47445664222704</v>
+        <v>6.532366117645372</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444522171834366</v>
+        <v>0.7445079266878462</v>
       </c>
       <c r="G4" t="n">
-        <v>33.29185825527864</v>
+        <v>33.40393804094575</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24480199043808</v>
+        <v>34.24736462764092</v>
       </c>
       <c r="I4" t="n">
-        <v>5.492292557447525</v>
+        <v>5.507106217874858</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652826357396479</v>
+        <v>4.653174541799038</v>
       </c>
       <c r="K4" t="n">
-        <v>12.91399326806168</v>
+        <v>12.72008070349772</v>
       </c>
       <c r="L4" t="n">
-        <v>44.29679803235765</v>
+        <v>44.3144416892456</v>
       </c>
       <c r="M4" t="n">
-        <v>99.8173076461276</v>
+        <v>99.81681507374087</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.8948079424016</v>
+        <v>86.32986085032557</v>
       </c>
       <c r="C5" t="n">
-        <v>42.26770544787609</v>
+        <v>42.68709132660449</v>
       </c>
       <c r="D5" t="n">
-        <v>2.127045508778485</v>
+        <v>2.145842737473609</v>
       </c>
       <c r="E5" t="n">
-        <v>7.065985995162385</v>
+        <v>7.162617181886427</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457768427798288</v>
+        <v>0.7458295250234093</v>
       </c>
       <c r="G5" t="n">
-        <v>32.40410526528559</v>
+        <v>32.70857701748152</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30573476787212</v>
+        <v>34.30815815107682</v>
       </c>
       <c r="I5" t="n">
-        <v>4.58505429514926</v>
+        <v>4.59740170598746</v>
       </c>
       <c r="J5" t="n">
-        <v>4.66110526737393</v>
+        <v>4.661434531396307</v>
       </c>
       <c r="K5" t="n">
-        <v>14.1051920575984</v>
+        <v>13.67013914967443</v>
       </c>
       <c r="L5" t="n">
-        <v>43.47453881237416</v>
+        <v>43.48979435100234</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84743631784866</v>
+        <v>99.84702482728127</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.64987736660906</v>
+        <v>85.06929710386854</v>
       </c>
       <c r="C6" t="n">
-        <v>41.73479613276225</v>
+        <v>42.14083073012844</v>
       </c>
       <c r="D6" t="n">
-        <v>2.066495915487973</v>
+        <v>2.084594149369136</v>
       </c>
       <c r="E6" t="n">
-        <v>7.502614608410798</v>
+        <v>7.597663282008483</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469006154503527</v>
+        <v>0.7469508438909229</v>
       </c>
       <c r="G6" t="n">
-        <v>31.48167300576956</v>
+        <v>31.77497916977261</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35742831071622</v>
+        <v>34.35973881898245</v>
       </c>
       <c r="I6" t="n">
-        <v>3.826636064209451</v>
+        <v>3.83692806552668</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668128846564704</v>
+        <v>4.668442774318268</v>
       </c>
       <c r="K6" t="n">
-        <v>15.35012263339096</v>
+        <v>14.93070289613144</v>
       </c>
       <c r="L6" t="n">
-        <v>42.7877186145371</v>
+        <v>42.80076077079602</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87263738069029</v>
+        <v>99.87229439705591</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.2881040354014</v>
+        <v>83.58804263756721</v>
       </c>
       <c r="C7" t="n">
-        <v>40.96738804505125</v>
+        <v>41.2558396545074</v>
       </c>
       <c r="D7" t="n">
-        <v>2.000497374328133</v>
+        <v>2.012678557466764</v>
       </c>
       <c r="E7" t="n">
-        <v>7.795156868694388</v>
+        <v>7.869141532366112</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478550565181032</v>
+        <v>0.7479044809858409</v>
       </c>
       <c r="G7" t="n">
-        <v>30.47622969660081</v>
+        <v>30.67878668771498</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40133259983275</v>
+        <v>34.40360612534868</v>
       </c>
       <c r="I7" t="n">
-        <v>3.192938336189072</v>
+        <v>3.201522247523329</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674094103238145</v>
+        <v>4.674403006161506</v>
       </c>
       <c r="K7" t="n">
-        <v>16.71189596459859</v>
+        <v>16.41195736243278</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21442054412213</v>
+        <v>42.22562164790628</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89370455377198</v>
+        <v>99.89341866484648</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.19038801857855</v>
+        <v>88.43543404588354</v>
       </c>
       <c r="C8" t="n">
-        <v>43.24081742484405</v>
+        <v>43.54322930653209</v>
       </c>
       <c r="D8" t="n">
-        <v>2.004804958387543</v>
+        <v>2.016956136937727</v>
       </c>
       <c r="E8" t="n">
-        <v>9.612343378097481</v>
+        <v>9.692099822179731</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494653803113493</v>
+        <v>0.7494940149142657</v>
       </c>
       <c r="G8" t="n">
-        <v>30.96731228106827</v>
+        <v>31.17722248753626</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47540749432207</v>
+        <v>34.47672468605622</v>
       </c>
       <c r="I8" t="n">
-        <v>5.696895899445912</v>
+        <v>5.638599305045179</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684158626945933</v>
+        <v>4.684337593214161</v>
       </c>
       <c r="K8" t="n">
-        <v>11.80961198142143</v>
+        <v>11.56456595411646</v>
       </c>
       <c r="L8" t="n">
-        <v>44.76008208113247</v>
+        <v>44.70465004232431</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81051148739795</v>
+        <v>99.81244530297286</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.47766290681201</v>
+        <v>86.49608914292946</v>
       </c>
       <c r="C9" t="n">
-        <v>42.41243642768781</v>
+        <v>42.47956635098129</v>
       </c>
       <c r="D9" t="n">
-        <v>1.927700268829615</v>
+        <v>1.929241577117689</v>
       </c>
       <c r="E9" t="n">
-        <v>10.03533926791154</v>
+        <v>10.05516363495412</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508393554260042</v>
+        <v>0.7508536662910862</v>
       </c>
       <c r="G9" t="n">
-        <v>29.77631113660003</v>
+        <v>29.82136932998687</v>
       </c>
       <c r="H9" t="n">
-        <v>34.5386103495962</v>
+        <v>34.53926864938995</v>
       </c>
       <c r="I9" t="n">
-        <v>4.756116557036118</v>
+        <v>4.707356870870456</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692745971412527</v>
+        <v>4.692835414319289</v>
       </c>
       <c r="K9" t="n">
-        <v>13.52233709318798</v>
+        <v>13.50391085707053</v>
       </c>
       <c r="L9" t="n">
-        <v>43.90697937080627</v>
+        <v>43.85989503347469</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84175289168206</v>
+        <v>99.84337224152652</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.59951473080163</v>
+        <v>84.39726213848913</v>
       </c>
       <c r="C10" t="n">
-        <v>41.27261359678956</v>
+        <v>41.1116007693081</v>
       </c>
       <c r="D10" t="n">
-        <v>1.843838839507118</v>
+        <v>1.835228866573595</v>
       </c>
       <c r="E10" t="n">
-        <v>10.26037327578446</v>
+        <v>10.21998559963698</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520137333759808</v>
+        <v>0.7520187978385805</v>
       </c>
       <c r="G10" t="n">
-        <v>28.48094169963733</v>
+        <v>28.36816212353779</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59263173529511</v>
+        <v>34.59286470057469</v>
       </c>
       <c r="I10" t="n">
-        <v>3.969629613601736</v>
+        <v>3.928884563836359</v>
       </c>
       <c r="J10" t="n">
-        <v>4.70008583359988</v>
+        <v>4.700117486491128</v>
       </c>
       <c r="K10" t="n">
-        <v>15.40048526919839</v>
+        <v>15.60273786151087</v>
       </c>
       <c r="L10" t="n">
-        <v>43.19478678520549</v>
+        <v>43.15490145610129</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86788565119343</v>
+        <v>99.86924008692027</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.54338468252963</v>
+        <v>82.14606267404474</v>
       </c>
       <c r="C11" t="n">
-        <v>39.83237494636649</v>
+        <v>39.46987433478649</v>
       </c>
       <c r="D11" t="n">
-        <v>1.752767524744024</v>
+        <v>1.735329472526997</v>
       </c>
       <c r="E11" t="n">
-        <v>10.30566549234975</v>
+        <v>10.21007220403953</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530196721187684</v>
+        <v>0.753019226397228</v>
       </c>
       <c r="G11" t="n">
-        <v>27.0742044345896</v>
+        <v>26.82396114785887</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63890491746334</v>
+        <v>34.63888441427247</v>
       </c>
       <c r="I11" t="n">
-        <v>3.312449690521844</v>
+        <v>3.278426043966953</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706372950742303</v>
+        <v>4.706370164982674</v>
       </c>
       <c r="K11" t="n">
-        <v>17.45661531747037</v>
+        <v>17.85393732595527</v>
       </c>
       <c r="L11" t="n">
-        <v>42.60074224689644</v>
+        <v>42.56705265692946</v>
       </c>
       <c r="M11" t="n">
-        <v>99.8897325107333</v>
+        <v>99.89086431767122</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>80.37714230045735</v>
+        <v>79.7603705555771</v>
       </c>
       <c r="C12" t="n">
-        <v>38.17947719874679</v>
+        <v>37.59202688290595</v>
       </c>
       <c r="D12" t="n">
-        <v>1.6576382013291</v>
+        <v>1.630406643072035</v>
       </c>
       <c r="E12" t="n">
-        <v>10.20692776632</v>
+        <v>10.04860037230993</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538826864312842</v>
+        <v>0.7538799781915341</v>
       </c>
       <c r="G12" t="n">
-        <v>25.60478495168586</v>
+        <v>25.20211011300904</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67860357583907</v>
+        <v>34.67847899681055</v>
       </c>
       <c r="I12" t="n">
-        <v>2.763538328656504</v>
+        <v>2.7351445884869</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711766790195526</v>
+        <v>4.711749863697087</v>
       </c>
       <c r="K12" t="n">
-        <v>19.62285769954265</v>
+        <v>20.23962944442291</v>
       </c>
       <c r="L12" t="n">
-        <v>42.10565261030719</v>
+        <v>42.07727628256094</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90798750859663</v>
+        <v>99.9089326098898</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>78.22121243572268</v>
+        <v>77.35629089907923</v>
       </c>
       <c r="C13" t="n">
-        <v>36.45112850890051</v>
+        <v>35.61079864293005</v>
       </c>
       <c r="D13" t="n">
-        <v>1.563794884055683</v>
+        <v>1.525627701930085</v>
       </c>
       <c r="E13" t="n">
-        <v>10.01328819422136</v>
+        <v>9.783076443617182</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546232607304015</v>
+        <v>0.754621136730124</v>
       </c>
       <c r="G13" t="n">
-        <v>24.15522982197658</v>
+        <v>23.58248324053238</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71266999359847</v>
+        <v>34.71257228958569</v>
       </c>
       <c r="I13" t="n">
-        <v>2.30521090157518</v>
+        <v>2.281527982120477</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716395379565009</v>
+        <v>4.716382104563275</v>
       </c>
       <c r="K13" t="n">
-        <v>21.77878756427734</v>
+        <v>22.64370910092081</v>
       </c>
       <c r="L13" t="n">
-        <v>41.69331897324835</v>
+        <v>41.66951601758006</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92323504642619</v>
+        <v>99.9240237614309</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.42672269959665</v>
+        <v>83.91604699627861</v>
       </c>
       <c r="C14" t="n">
-        <v>40.39553562052818</v>
+        <v>39.68668125415882</v>
       </c>
       <c r="D14" t="n">
-        <v>1.565517632850926</v>
+        <v>1.527403136566697</v>
       </c>
       <c r="E14" t="n">
-        <v>12.21329293213631</v>
+        <v>12.06139027572047</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554545886280307</v>
+        <v>0.7554993198556502</v>
       </c>
       <c r="G14" t="n">
-        <v>25.90577205790352</v>
+        <v>25.38857351749142</v>
       </c>
       <c r="H14" t="n">
-        <v>36.47484279407192</v>
+        <v>36.53161510115148</v>
       </c>
       <c r="I14" t="n">
-        <v>2.790251515080757</v>
+        <v>2.929694896395064</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721591178925192</v>
+        <v>4.721870749097814</v>
       </c>
       <c r="K14" t="n">
-        <v>15.57327730040335</v>
+        <v>16.08395300372141</v>
       </c>
       <c r="L14" t="n">
-        <v>43.93828104481823</v>
+        <v>44.13182276028483</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90709396574975</v>
+        <v>99.90245701816505</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.83300095797635</v>
+        <v>83.13886606116567</v>
       </c>
       <c r="C15" t="n">
-        <v>40.23385040254858</v>
+        <v>39.3625873834651</v>
       </c>
       <c r="D15" t="n">
-        <v>1.543522945034368</v>
+        <v>1.498414527794499</v>
       </c>
       <c r="E15" t="n">
-        <v>12.42959623592611</v>
+        <v>12.23977771004578</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7561536831691579</v>
+        <v>0.7562395643596553</v>
       </c>
       <c r="G15" t="n">
-        <v>25.54180977660819</v>
+        <v>24.90672337108078</v>
       </c>
       <c r="H15" t="n">
-        <v>36.50859646222041</v>
+        <v>36.56740908082869</v>
       </c>
       <c r="I15" t="n">
-        <v>2.327361335210896</v>
+        <v>2.443804529808427</v>
       </c>
       <c r="J15" t="n">
-        <v>4.725960519807237</v>
+        <v>4.726497277247846</v>
       </c>
       <c r="K15" t="n">
-        <v>16.16699904202365</v>
+        <v>16.86113393883431</v>
       </c>
       <c r="L15" t="n">
-        <v>43.52164356889774</v>
+        <v>43.69489826391185</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92249301346997</v>
+        <v>99.91861958621126</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>81.71855202247774</v>
+        <v>80.76787663307034</v>
       </c>
       <c r="C16" t="n">
-        <v>38.47987833512961</v>
+        <v>37.3695830409921</v>
       </c>
       <c r="D16" t="n">
-        <v>1.462085514070515</v>
+        <v>1.407665102840181</v>
       </c>
       <c r="E16" t="n">
-        <v>12.09730195088552</v>
+        <v>11.83819513381277</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7567523627378917</v>
+        <v>0.7568757001951663</v>
       </c>
       <c r="G16" t="n">
-        <v>24.19420469106922</v>
+        <v>23.39828176063489</v>
       </c>
       <c r="H16" t="n">
-        <v>36.53750189675254</v>
+        <v>36.59816896225303</v>
       </c>
       <c r="I16" t="n">
-        <v>1.941003339850223</v>
+        <v>2.038216847114519</v>
       </c>
       <c r="J16" t="n">
-        <v>4.729702267111823</v>
+        <v>4.730473126219789</v>
       </c>
       <c r="K16" t="n">
-        <v>18.28144797752226</v>
+        <v>19.23212336692966</v>
       </c>
       <c r="L16" t="n">
-        <v>43.17402476137006</v>
+        <v>43.33041013291689</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93535107402194</v>
+        <v>99.93211654083863</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>83.2951897481129</v>
+        <v>82.38179131903576</v>
       </c>
       <c r="C17" t="n">
-        <v>39.64985086608223</v>
+        <v>38.55058134990759</v>
       </c>
       <c r="D17" t="n">
-        <v>1.463200139682855</v>
+        <v>1.408821851012998</v>
       </c>
       <c r="E17" t="n">
-        <v>12.8354627870245</v>
+        <v>12.59242031935978</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7573292753449786</v>
+        <v>0.7574976624655128</v>
       </c>
       <c r="G17" t="n">
-        <v>24.62408585585656</v>
+        <v>23.82352044016511</v>
       </c>
       <c r="H17" t="n">
-        <v>36.97679301401789</v>
+        <v>37.03425464322632</v>
       </c>
       <c r="I17" t="n">
-        <v>1.905010705280004</v>
+        <v>2.030916012396586</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733307970906116</v>
+        <v>4.734360390409455</v>
       </c>
       <c r="K17" t="n">
-        <v>16.70481025188709</v>
+        <v>17.61820868096424</v>
       </c>
       <c r="L17" t="n">
-        <v>43.5818868980129</v>
+        <v>43.76356835318281</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93654801598223</v>
+        <v>99.93235838405464</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>81.25582487703508</v>
+        <v>80.09589978194452</v>
       </c>
       <c r="C18" t="n">
-        <v>37.90529800700886</v>
+        <v>36.57844040430058</v>
       </c>
       <c r="D18" t="n">
-        <v>1.387439042799939</v>
+        <v>1.324614462061473</v>
       </c>
       <c r="E18" t="n">
-        <v>12.43562964546909</v>
+        <v>12.12202300602386</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7578227991245634</v>
+        <v>0.7580315705191571</v>
       </c>
       <c r="G18" t="n">
-        <v>23.34910801544769</v>
+        <v>22.39955299498593</v>
       </c>
       <c r="H18" t="n">
-        <v>37.00088943711852</v>
+        <v>37.06035754465361</v>
       </c>
       <c r="I18" t="n">
-        <v>1.588543442546765</v>
+        <v>1.693622887955752</v>
       </c>
       <c r="J18" t="n">
-        <v>4.736392494528522</v>
+        <v>4.737697315744732</v>
       </c>
       <c r="K18" t="n">
-        <v>18.74417512296491</v>
+        <v>19.90410021805547</v>
       </c>
       <c r="L18" t="n">
-        <v>43.29760990599068</v>
+        <v>43.46104504396627</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94708303596444</v>
+        <v>99.94358566632232</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>80.44224073704872</v>
+        <v>79.19355583201718</v>
       </c>
       <c r="C19" t="n">
-        <v>37.33704639654196</v>
+        <v>35.93710348476806</v>
       </c>
       <c r="D19" t="n">
-        <v>1.357817111413055</v>
+        <v>1.292037930680835</v>
       </c>
       <c r="E19" t="n">
-        <v>12.39088011232974</v>
+        <v>12.05926867967666</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7582387273549684</v>
+        <v>0.758482148260442</v>
       </c>
       <c r="G19" t="n">
-        <v>22.85060274477091</v>
+        <v>21.8486759194648</v>
       </c>
       <c r="H19" t="n">
-        <v>37.0211972379458</v>
+        <v>37.08238640577643</v>
       </c>
       <c r="I19" t="n">
-        <v>1.324512757265696</v>
+        <v>1.412191321530265</v>
       </c>
       <c r="J19" t="n">
-        <v>4.738992045968553</v>
+        <v>4.740513426627762</v>
       </c>
       <c r="K19" t="n">
-        <v>19.55775926295128</v>
+        <v>20.8064441679828</v>
       </c>
       <c r="L19" t="n">
-        <v>43.06106813376935</v>
+        <v>43.20940726702813</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95587379326258</v>
+        <v>99.952954919779</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>78.13780398582426</v>
+        <v>76.71520247498543</v>
       </c>
       <c r="C20" t="n">
-        <v>35.23706204982001</v>
+        <v>33.67624900459684</v>
       </c>
       <c r="D20" t="n">
-        <v>1.272922942517268</v>
+        <v>1.201682849746087</v>
       </c>
       <c r="E20" t="n">
-        <v>11.80021763304697</v>
+        <v>11.41217527608962</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7585959203605993</v>
+        <v>0.7588701887951479</v>
       </c>
       <c r="G20" t="n">
-        <v>21.42192511765932</v>
+        <v>20.32074950636015</v>
       </c>
       <c r="H20" t="n">
-        <v>37.03863727659907</v>
+        <v>37.10135780685959</v>
       </c>
       <c r="I20" t="n">
-        <v>1.104280593387294</v>
+        <v>1.177428167165159</v>
       </c>
       <c r="J20" t="n">
-        <v>4.741224502253746</v>
+        <v>4.742938679969674</v>
       </c>
       <c r="K20" t="n">
-        <v>21.86219601417573</v>
+        <v>23.28479752501457</v>
       </c>
       <c r="L20" t="n">
-        <v>42.8639499149691</v>
+        <v>42.99972593367941</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96320797896485</v>
+        <v>99.96077246329082</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>83.34904842716787</v>
+        <v>82.4165942751513</v>
       </c>
       <c r="C21" t="n">
-        <v>38.5020963666606</v>
+        <v>37.22274252845217</v>
       </c>
       <c r="D21" t="n">
-        <v>1.273696599699303</v>
+        <v>1.202494243432405</v>
       </c>
       <c r="E21" t="n">
-        <v>13.55923883757581</v>
+        <v>13.32482700045611</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7590569798343866</v>
+        <v>0.7593825889513566</v>
       </c>
       <c r="G21" t="n">
-        <v>22.93350475598054</v>
+        <v>21.96117203115204</v>
       </c>
       <c r="H21" t="n">
-        <v>38.55970844116903</v>
+        <v>38.75311084171949</v>
       </c>
       <c r="I21" t="n">
-        <v>1.519736688943898</v>
+        <v>1.669466388493921</v>
       </c>
       <c r="J21" t="n">
-        <v>4.744106123964917</v>
+        <v>4.746141180945978</v>
       </c>
       <c r="K21" t="n">
-        <v>16.65095157283211</v>
+        <v>17.58340572484869</v>
       </c>
       <c r="L21" t="n">
-        <v>44.79632494102952</v>
+        <v>45.13824041665917</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94937288052223</v>
+        <v>99.94438866996003</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_13_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_13_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.04499765763666</v>
+        <v>45.43874762605349</v>
       </c>
       <c r="M2" t="n">
-        <v>100.1549536108869</v>
+        <v>99.13874074150746</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.06922421807596</v>
+        <v>88.02141310487914</v>
       </c>
       <c r="C3" t="n">
-        <v>45.93142542198285</v>
+        <v>45.92345983472444</v>
       </c>
       <c r="D3" t="n">
-        <v>2.22883601348164</v>
+        <v>2.228719452466743</v>
       </c>
       <c r="E3" t="n">
-        <v>5.710267582572784</v>
+        <v>5.703048200346449</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429453378272133</v>
+        <v>0.742906484155581</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97362403739398</v>
+        <v>33.97137097062519</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17548554005181</v>
+        <v>34.17369827115672</v>
       </c>
       <c r="I3" t="n">
-        <v>6.59465734532845</v>
+        <v>6.558504200156076</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643408361420082</v>
+        <v>4.643165525972381</v>
       </c>
       <c r="K3" t="n">
-        <v>11.93077578192404</v>
+        <v>11.97858689512086</v>
       </c>
       <c r="L3" t="n">
-        <v>48.90109560912236</v>
+        <v>48.86253542273035</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7632968130293</v>
+        <v>106.7645821525757</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.27991929650229</v>
+        <v>87.04420478441141</v>
       </c>
       <c r="C4" t="n">
-        <v>42.78229268099756</v>
+        <v>42.57974014825901</v>
       </c>
       <c r="D4" t="n">
-        <v>2.191461823908504</v>
+        <v>2.181309681763353</v>
       </c>
       <c r="E4" t="n">
-        <v>6.532366117645372</v>
+        <v>6.494545656873542</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445079266878462</v>
+        <v>0.7444646242526864</v>
       </c>
       <c r="G4" t="n">
-        <v>33.40393804094575</v>
+        <v>33.24872510040829</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24736462764092</v>
+        <v>34.24537271562357</v>
       </c>
       <c r="I4" t="n">
-        <v>5.507106217874858</v>
+        <v>5.476883103910671</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653174541799038</v>
+        <v>4.65290390157929</v>
       </c>
       <c r="K4" t="n">
-        <v>12.72008070349772</v>
+        <v>12.95579521558859</v>
       </c>
       <c r="L4" t="n">
-        <v>44.3144416892456</v>
+        <v>44.28228396392583</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81681507374087</v>
+        <v>99.81781932777344</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.32986085032557</v>
+        <v>85.85004708375452</v>
       </c>
       <c r="C5" t="n">
-        <v>42.68709132660449</v>
+        <v>42.23556557151744</v>
       </c>
       <c r="D5" t="n">
-        <v>2.145842737473609</v>
+        <v>2.122940485919814</v>
       </c>
       <c r="E5" t="n">
-        <v>7.162617181886427</v>
+        <v>7.082788115429306</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458295250234093</v>
+        <v>0.7457862387644517</v>
       </c>
       <c r="G5" t="n">
-        <v>32.70857701748152</v>
+        <v>32.35902962839037</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30815815107682</v>
+        <v>34.30616698316478</v>
       </c>
       <c r="I5" t="n">
-        <v>4.59740170598746</v>
+        <v>4.57217163980797</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661434531396307</v>
+        <v>4.661163992277823</v>
       </c>
       <c r="K5" t="n">
-        <v>13.67013914967443</v>
+        <v>14.1499529162455</v>
       </c>
       <c r="L5" t="n">
-        <v>43.48979435100234</v>
+        <v>43.46234587046176</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84702482728127</v>
+        <v>99.8478643582247</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>85.06929710386854</v>
+        <v>84.46329015503487</v>
       </c>
       <c r="C6" t="n">
-        <v>42.14083073012844</v>
+        <v>41.55881137864651</v>
       </c>
       <c r="D6" t="n">
-        <v>2.084594149369136</v>
+        <v>2.055201534481527</v>
       </c>
       <c r="E6" t="n">
-        <v>7.597663282008483</v>
+        <v>7.492770099044892</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469508438909229</v>
+        <v>0.7469093426292617</v>
       </c>
       <c r="G6" t="n">
-        <v>31.77497916977261</v>
+        <v>31.32651517444048</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35973881898245</v>
+        <v>34.35782976094604</v>
       </c>
       <c r="I6" t="n">
-        <v>3.83692806552668</v>
+        <v>3.815880852059757</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668442774318268</v>
+        <v>4.668183391432885</v>
       </c>
       <c r="K6" t="n">
-        <v>14.93070289613144</v>
+        <v>15.53670984496515</v>
       </c>
       <c r="L6" t="n">
-        <v>42.80076077079602</v>
+        <v>42.77747400861591</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87229439705591</v>
+        <v>99.87299523222757</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.58804263756721</v>
+        <v>82.700425596755</v>
       </c>
       <c r="C7" t="n">
-        <v>41.2558396545074</v>
+        <v>40.38851504399129</v>
       </c>
       <c r="D7" t="n">
-        <v>2.012678557466764</v>
+        <v>1.969087078113076</v>
       </c>
       <c r="E7" t="n">
-        <v>7.869141532366112</v>
+        <v>7.709481119593386</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479044809858409</v>
+        <v>0.7478678808666129</v>
       </c>
       <c r="G7" t="n">
-        <v>30.67878668771498</v>
+        <v>30.01391114077061</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40360612534868</v>
+        <v>34.40192251986419</v>
       </c>
       <c r="I7" t="n">
-        <v>3.201522247523329</v>
+        <v>3.183981602130801</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674403006161506</v>
+        <v>4.674174255416331</v>
       </c>
       <c r="K7" t="n">
-        <v>16.41195736243278</v>
+        <v>17.29957440324499</v>
       </c>
       <c r="L7" t="n">
-        <v>42.22562164790628</v>
+        <v>42.20591386242872</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89341866484648</v>
+        <v>99.894003309665</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.43543404588354</v>
+        <v>87.54500865174057</v>
       </c>
       <c r="C8" t="n">
-        <v>43.54322930653209</v>
+        <v>42.69293899231418</v>
       </c>
       <c r="D8" t="n">
-        <v>2.016956136937727</v>
+        <v>1.973286816872502</v>
       </c>
       <c r="E8" t="n">
-        <v>9.692099822179731</v>
+        <v>9.542053460567756</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494940149142657</v>
+        <v>0.7494629600081687</v>
       </c>
       <c r="G8" t="n">
-        <v>31.17722248753626</v>
+        <v>30.51919276937404</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47672468605622</v>
+        <v>34.47529616037576</v>
       </c>
       <c r="I8" t="n">
-        <v>5.638599305045179</v>
+        <v>5.601572984491291</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684337593214161</v>
+        <v>4.684143500051054</v>
       </c>
       <c r="K8" t="n">
-        <v>11.56456595411646</v>
+        <v>12.45499134825943</v>
       </c>
       <c r="L8" t="n">
-        <v>44.70465004232431</v>
+        <v>44.6657479534862</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81244530297286</v>
+        <v>99.8136782940598</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.49608914292946</v>
+        <v>85.39766747623608</v>
       </c>
       <c r="C9" t="n">
-        <v>42.47956635098129</v>
+        <v>41.41465107916401</v>
       </c>
       <c r="D9" t="n">
-        <v>1.929241577117689</v>
+        <v>1.875899120076067</v>
       </c>
       <c r="E9" t="n">
-        <v>10.05516363495412</v>
+        <v>9.850540532828614</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508536662910862</v>
+        <v>0.7508310154364707</v>
       </c>
       <c r="G9" t="n">
-        <v>29.82136932998687</v>
+        <v>29.01297792696891</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53926864938995</v>
+        <v>34.53822671007764</v>
       </c>
       <c r="I9" t="n">
-        <v>4.707356870870456</v>
+        <v>4.676498324370445</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692835414319289</v>
+        <v>4.69269384647794</v>
       </c>
       <c r="K9" t="n">
-        <v>13.50391085707053</v>
+        <v>14.6023325237639</v>
       </c>
       <c r="L9" t="n">
-        <v>43.85989503347469</v>
+        <v>43.82741714750289</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84337224152652</v>
+        <v>99.84440075043081</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.39726213848913</v>
+        <v>83.07298954605106</v>
       </c>
       <c r="C10" t="n">
-        <v>41.1116007693081</v>
+        <v>39.81508432128756</v>
       </c>
       <c r="D10" t="n">
-        <v>1.835228866573595</v>
+        <v>1.771626645687846</v>
       </c>
       <c r="E10" t="n">
-        <v>10.21998559963698</v>
+        <v>9.953525875243681</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520187978385805</v>
+        <v>0.7520069422477919</v>
       </c>
       <c r="G10" t="n">
-        <v>28.36816212353779</v>
+        <v>27.40028193205144</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59286470057469</v>
+        <v>34.59231934339842</v>
       </c>
       <c r="I10" t="n">
-        <v>3.928884563836359</v>
+        <v>3.903185418373167</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700117486491128</v>
+        <v>4.700043389048698</v>
       </c>
       <c r="K10" t="n">
-        <v>15.60273786151087</v>
+        <v>16.92701045394896</v>
       </c>
       <c r="L10" t="n">
-        <v>43.15490145610129</v>
+        <v>43.12800249353096</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86924008692027</v>
+        <v>99.87009726876748</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.14606267404474</v>
+        <v>80.64662475412094</v>
       </c>
       <c r="C11" t="n">
-        <v>39.46987433478649</v>
+        <v>37.99318568918584</v>
       </c>
       <c r="D11" t="n">
-        <v>1.735329472526997</v>
+        <v>1.663996261922268</v>
       </c>
       <c r="E11" t="n">
-        <v>10.21007220403953</v>
+        <v>9.891665221526383</v>
       </c>
       <c r="F11" t="n">
-        <v>0.753019226397228</v>
+        <v>0.7530193060234286</v>
       </c>
       <c r="G11" t="n">
-        <v>26.82396114785887</v>
+        <v>25.73565193407198</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63888441427247</v>
+        <v>34.63888807707771</v>
       </c>
       <c r="I11" t="n">
-        <v>3.278426043966953</v>
+        <v>3.257033290852751</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706370164982674</v>
+        <v>4.706370662646427</v>
       </c>
       <c r="K11" t="n">
-        <v>17.85393732595527</v>
+        <v>19.35337524587905</v>
       </c>
       <c r="L11" t="n">
-        <v>42.56705265692946</v>
+        <v>42.5450172477581</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89086431767122</v>
+        <v>99.89157818282298</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.7603705555771</v>
+        <v>78.19643928069601</v>
       </c>
       <c r="C12" t="n">
-        <v>37.59202688290595</v>
+        <v>36.04651298495979</v>
       </c>
       <c r="D12" t="n">
-        <v>1.630406643072035</v>
+        <v>1.556466013175444</v>
       </c>
       <c r="E12" t="n">
-        <v>10.04860037230993</v>
+        <v>9.705338836491459</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538799781915341</v>
+        <v>0.7538915572702418</v>
       </c>
       <c r="G12" t="n">
-        <v>25.20211011300904</v>
+        <v>24.07257064148808</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67847899681055</v>
+        <v>34.67901163443112</v>
       </c>
       <c r="I12" t="n">
-        <v>2.7351445884869</v>
+        <v>2.717338364900661</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711749863697087</v>
+        <v>4.71182223293901</v>
       </c>
       <c r="K12" t="n">
-        <v>20.23962944442291</v>
+        <v>21.80356071930398</v>
       </c>
       <c r="L12" t="n">
-        <v>42.07727628256094</v>
+        <v>42.05945314876809</v>
       </c>
       <c r="M12" t="n">
-        <v>99.9089326098898</v>
+        <v>99.90952685303188</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.35629089907923</v>
+        <v>75.8763899929348</v>
       </c>
       <c r="C13" t="n">
-        <v>35.61079864293005</v>
+        <v>34.14562586690023</v>
       </c>
       <c r="D13" t="n">
-        <v>1.525627701930085</v>
+        <v>1.455716853613921</v>
       </c>
       <c r="E13" t="n">
-        <v>9.783076443617182</v>
+        <v>9.454901699590266</v>
       </c>
       <c r="F13" t="n">
-        <v>0.754621136730124</v>
+        <v>0.754642273300033</v>
       </c>
       <c r="G13" t="n">
-        <v>23.58248324053238</v>
+        <v>22.51436683871612</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71257228958569</v>
+        <v>34.71354457180151</v>
       </c>
       <c r="I13" t="n">
-        <v>2.281527982120477</v>
+        <v>2.266703547787753</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716382104563275</v>
+        <v>4.716514208125205</v>
       </c>
       <c r="K13" t="n">
-        <v>22.64370910092081</v>
+        <v>24.12361000706518</v>
       </c>
       <c r="L13" t="n">
-        <v>41.66951601758006</v>
+        <v>41.65528250478735</v>
       </c>
       <c r="M13" t="n">
-        <v>99.9240237614309</v>
+        <v>99.92451837875277</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.91604699627861</v>
+        <v>83.02754568898116</v>
       </c>
       <c r="C14" t="n">
-        <v>39.68668125415882</v>
+        <v>38.62530524965218</v>
       </c>
       <c r="D14" t="n">
-        <v>1.527403136566697</v>
+        <v>1.457410191578917</v>
       </c>
       <c r="E14" t="n">
-        <v>12.06139027572047</v>
+        <v>11.93277538993026</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554993198556502</v>
+        <v>0.755520098138151</v>
       </c>
       <c r="G14" t="n">
-        <v>25.38857351749142</v>
+        <v>24.52452980188779</v>
       </c>
       <c r="H14" t="n">
-        <v>36.53161510115148</v>
+        <v>36.73789802177415</v>
       </c>
       <c r="I14" t="n">
-        <v>2.929694896395064</v>
+        <v>2.897411572308443</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721870749097814</v>
+        <v>4.722000613363443</v>
       </c>
       <c r="K14" t="n">
-        <v>16.08395300372141</v>
+        <v>16.97245431101886</v>
       </c>
       <c r="L14" t="n">
-        <v>44.13182276028483</v>
+        <v>44.30577226855048</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90245701816505</v>
+        <v>99.90353182922152</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.13886606116567</v>
+        <v>82.33857478509481</v>
       </c>
       <c r="C15" t="n">
-        <v>39.3625873834651</v>
+        <v>38.38368285158052</v>
       </c>
       <c r="D15" t="n">
-        <v>1.498414527794499</v>
+        <v>1.432326781235835</v>
       </c>
       <c r="E15" t="n">
-        <v>12.23977771004578</v>
+        <v>12.13021303016755</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562395643596553</v>
+        <v>0.7562593204800158</v>
       </c>
       <c r="G15" t="n">
-        <v>24.90672337108078</v>
+        <v>24.10243940616643</v>
       </c>
       <c r="H15" t="n">
-        <v>36.56740908082869</v>
+        <v>36.77384342557978</v>
       </c>
       <c r="I15" t="n">
-        <v>2.443804529808427</v>
+        <v>2.416872068465086</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726497277247846</v>
+        <v>4.726620753000098</v>
       </c>
       <c r="K15" t="n">
-        <v>16.86113393883431</v>
+        <v>17.66142521490519</v>
       </c>
       <c r="L15" t="n">
-        <v>43.69489826391185</v>
+        <v>43.87440827872796</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91861958621126</v>
+        <v>99.91951634521368</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.76787663307034</v>
+        <v>79.90023746448814</v>
       </c>
       <c r="C16" t="n">
-        <v>37.3695830409921</v>
+        <v>36.31857789361887</v>
       </c>
       <c r="D16" t="n">
-        <v>1.407665102840181</v>
+        <v>1.340728031176588</v>
       </c>
       <c r="E16" t="n">
-        <v>11.83819513381277</v>
+        <v>11.6904325688488</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568757001951663</v>
+        <v>0.756895293799992</v>
       </c>
       <c r="G16" t="n">
-        <v>23.39828176063489</v>
+        <v>22.56106396593435</v>
       </c>
       <c r="H16" t="n">
-        <v>36.59816896225303</v>
+        <v>36.80476824549051</v>
       </c>
       <c r="I16" t="n">
-        <v>2.038216847114519</v>
+        <v>2.015753772987951</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730473126219789</v>
+        <v>4.730595586249949</v>
       </c>
       <c r="K16" t="n">
-        <v>19.23212336692966</v>
+        <v>20.09976253551186</v>
       </c>
       <c r="L16" t="n">
-        <v>43.33041013291689</v>
+        <v>43.51452423563412</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93211654083863</v>
+        <v>99.93286466476484</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.38179131903576</v>
+        <v>81.74970287713352</v>
       </c>
       <c r="C17" t="n">
-        <v>38.55058134990759</v>
+        <v>37.65674779698418</v>
       </c>
       <c r="D17" t="n">
-        <v>1.408821851012998</v>
+        <v>1.341824460902093</v>
       </c>
       <c r="E17" t="n">
-        <v>12.59242031935978</v>
+        <v>12.52147607546674</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574976624655128</v>
+        <v>0.7575142728023841</v>
       </c>
       <c r="G17" t="n">
-        <v>23.82352044016511</v>
+        <v>23.06672818019379</v>
       </c>
       <c r="H17" t="n">
-        <v>37.03425464322632</v>
+        <v>37.32208077350953</v>
       </c>
       <c r="I17" t="n">
-        <v>2.030916012396586</v>
+        <v>2.005614909244085</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734360390409455</v>
+        <v>4.7344642050149</v>
       </c>
       <c r="K17" t="n">
-        <v>17.61820868096424</v>
+        <v>18.25029712286651</v>
       </c>
       <c r="L17" t="n">
-        <v>43.76356835318281</v>
+        <v>44.02615587734943</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93235838405464</v>
+        <v>99.9332007972001</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.09589978194452</v>
+        <v>79.42634784764819</v>
       </c>
       <c r="C18" t="n">
-        <v>36.57844040430058</v>
+        <v>35.64274558616361</v>
       </c>
       <c r="D18" t="n">
-        <v>1.324614462061473</v>
+        <v>1.258289720058707</v>
       </c>
       <c r="E18" t="n">
-        <v>12.12202300602386</v>
+        <v>12.0207097809067</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580315705191571</v>
+        <v>0.7580459842450159</v>
       </c>
       <c r="G18" t="n">
-        <v>22.39955299498593</v>
+        <v>21.63071831692009</v>
       </c>
       <c r="H18" t="n">
-        <v>37.06035754465361</v>
+        <v>37.34827774183422</v>
       </c>
       <c r="I18" t="n">
-        <v>1.693622887955752</v>
+        <v>1.672518902152126</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737697315744732</v>
+        <v>4.737787401531349</v>
       </c>
       <c r="K18" t="n">
-        <v>19.90410021805547</v>
+        <v>20.5736521523518</v>
       </c>
       <c r="L18" t="n">
-        <v>43.46104504396627</v>
+        <v>43.72789073622783</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94358566632232</v>
+        <v>99.94428847474325</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.19355583201718</v>
+        <v>78.5521604218787</v>
       </c>
       <c r="C19" t="n">
-        <v>35.93710348476806</v>
+        <v>35.02251445471651</v>
       </c>
       <c r="D19" t="n">
-        <v>1.292037930680835</v>
+        <v>1.227367534136087</v>
       </c>
       <c r="E19" t="n">
-        <v>12.05926867967666</v>
+        <v>11.95827727838219</v>
       </c>
       <c r="F19" t="n">
-        <v>0.758482148260442</v>
+        <v>0.7584956340007701</v>
       </c>
       <c r="G19" t="n">
-        <v>21.8486759194648</v>
+        <v>21.09914829550688</v>
       </c>
       <c r="H19" t="n">
-        <v>37.08238640577643</v>
+        <v>37.37043160098457</v>
       </c>
       <c r="I19" t="n">
-        <v>1.412191321530265</v>
+        <v>1.397842366363381</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740513426627762</v>
+        <v>4.740597712504813</v>
       </c>
       <c r="K19" t="n">
-        <v>20.8064441679828</v>
+        <v>21.44783957812133</v>
       </c>
       <c r="L19" t="n">
-        <v>43.20940726702813</v>
+        <v>43.48307884381389</v>
       </c>
       <c r="M19" t="n">
-        <v>99.952954919779</v>
+        <v>99.9534328766517</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.71520247498543</v>
+        <v>76.01772963598033</v>
       </c>
       <c r="C20" t="n">
-        <v>33.67624900459684</v>
+        <v>32.7030027292336</v>
       </c>
       <c r="D20" t="n">
-        <v>1.201682849746087</v>
+        <v>1.137217863608562</v>
       </c>
       <c r="E20" t="n">
-        <v>11.41217527608962</v>
+        <v>11.27419042944118</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7588701887951479</v>
+        <v>0.7588832625698712</v>
       </c>
       <c r="G20" t="n">
-        <v>20.32074950636015</v>
+        <v>19.54942401622638</v>
       </c>
       <c r="H20" t="n">
-        <v>37.10135780685959</v>
+        <v>37.38952972927804</v>
       </c>
       <c r="I20" t="n">
-        <v>1.177428167165159</v>
+        <v>1.165463943794604</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742938679969674</v>
+        <v>4.743020391061694</v>
       </c>
       <c r="K20" t="n">
-        <v>23.28479752501457</v>
+        <v>23.98227036401968</v>
       </c>
       <c r="L20" t="n">
-        <v>42.99972593367941</v>
+        <v>43.27589795212554</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96077246329082</v>
+        <v>99.96117104537882</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.4165942751513</v>
+        <v>81.84435317329992</v>
       </c>
       <c r="C21" t="n">
-        <v>37.22274252845217</v>
+        <v>36.36039246428422</v>
       </c>
       <c r="D21" t="n">
-        <v>1.202494243432405</v>
+        <v>1.137964812534589</v>
       </c>
       <c r="E21" t="n">
-        <v>13.32482700045611</v>
+        <v>13.23752242926561</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7593825889513566</v>
+        <v>0.7593817132679259</v>
       </c>
       <c r="G21" t="n">
-        <v>21.96117203115204</v>
+        <v>21.24940578979769</v>
       </c>
       <c r="H21" t="n">
-        <v>38.75311084171949</v>
+        <v>39.10122926444014</v>
       </c>
       <c r="I21" t="n">
-        <v>1.669466388493921</v>
+        <v>1.612713456069441</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746141180945978</v>
+        <v>4.746135707924537</v>
       </c>
       <c r="K21" t="n">
-        <v>17.58340572484869</v>
+        <v>18.15564682670007</v>
       </c>
       <c r="L21" t="n">
-        <v>45.13824041665917</v>
+        <v>45.43023887945582</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94438866996003</v>
+        <v>99.94627817044011</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_13_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_13_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.43874762605349</v>
+        <v>43.97607301377628</v>
       </c>
       <c r="M2" t="n">
-        <v>99.13874074150746</v>
+        <v>94.46315087097406</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.02141310487914</v>
+        <v>81.45471283066394</v>
       </c>
       <c r="C3" t="n">
-        <v>45.92345983472444</v>
+        <v>43.21026838621951</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228719452466743</v>
+        <v>2.178870747795304</v>
       </c>
       <c r="E3" t="n">
-        <v>5.703048200346449</v>
+        <v>4.150467103490376</v>
       </c>
       <c r="F3" t="n">
-        <v>0.742906484155581</v>
+        <v>0.737617314623348</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97137097062519</v>
+        <v>32.7738474980877</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17369827115672</v>
+        <v>33.930396472674</v>
       </c>
       <c r="I3" t="n">
-        <v>6.558504200156076</v>
+        <v>3.073405477597284</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643165525972381</v>
+        <v>4.610108216395925</v>
       </c>
       <c r="K3" t="n">
-        <v>11.97858689512086</v>
+        <v>18.54528716933605</v>
       </c>
       <c r="L3" t="n">
-        <v>48.86253542273035</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7645821525757</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.04420478441141</v>
+        <v>88.49056108232399</v>
       </c>
       <c r="C4" t="n">
-        <v>42.57974014825901</v>
+        <v>42.76347294070222</v>
       </c>
       <c r="D4" t="n">
-        <v>2.181309681763353</v>
+        <v>2.184593890106048</v>
       </c>
       <c r="E4" t="n">
-        <v>6.494545656873542</v>
+        <v>6.502324028605144</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444646242526864</v>
+        <v>0.7395547810227338</v>
       </c>
       <c r="G4" t="n">
-        <v>33.24872510040829</v>
+        <v>33.44932514210753</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24537271562357</v>
+        <v>34.01951992704575</v>
       </c>
       <c r="I4" t="n">
-        <v>5.476883103910671</v>
+        <v>6.97302593204471</v>
       </c>
       <c r="J4" t="n">
-        <v>4.65290390157929</v>
+        <v>4.622217381392087</v>
       </c>
       <c r="K4" t="n">
-        <v>12.95579521558859</v>
+        <v>11.50943891767599</v>
       </c>
       <c r="L4" t="n">
-        <v>44.28228396392583</v>
+        <v>45.4952628689588</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81781932777344</v>
+        <v>99.76817472733703</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.85004708375452</v>
+        <v>87.38039127186303</v>
       </c>
       <c r="C5" t="n">
-        <v>42.23556557151744</v>
+        <v>42.73410385527559</v>
       </c>
       <c r="D5" t="n">
-        <v>2.122940485919814</v>
+        <v>2.131761525316711</v>
       </c>
       <c r="E5" t="n">
-        <v>7.082788115429306</v>
+        <v>7.315698792409886</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457862387644517</v>
+        <v>0.7411977861091678</v>
       </c>
       <c r="G5" t="n">
-        <v>32.35902962839037</v>
+        <v>32.64038442508523</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30616698316478</v>
+        <v>34.09509816102171</v>
       </c>
       <c r="I5" t="n">
-        <v>4.57217163980797</v>
+        <v>5.823764418738035</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661163992277823</v>
+        <v>4.632486163182299</v>
       </c>
       <c r="K5" t="n">
-        <v>14.1499529162455</v>
+        <v>12.61960872813696</v>
       </c>
       <c r="L5" t="n">
-        <v>43.46234587046176</v>
+        <v>44.45259225180843</v>
       </c>
       <c r="M5" t="n">
-        <v>99.8478643582247</v>
+        <v>99.80630483522097</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.46329015503487</v>
+        <v>86.01870337975802</v>
       </c>
       <c r="C6" t="n">
-        <v>41.55881137864651</v>
+        <v>42.27621080608516</v>
       </c>
       <c r="D6" t="n">
-        <v>2.055201534481527</v>
+        <v>2.066678341673732</v>
       </c>
       <c r="E6" t="n">
-        <v>7.492770099044892</v>
+        <v>7.902728990042108</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469093426292617</v>
+        <v>0.7425943475444732</v>
       </c>
       <c r="G6" t="n">
-        <v>31.32651517444048</v>
+        <v>31.64386576739922</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35782976094604</v>
+        <v>34.15933998704576</v>
       </c>
       <c r="I6" t="n">
-        <v>3.815880852059757</v>
+        <v>4.862281273899772</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668183391432885</v>
+        <v>4.641214672152958</v>
       </c>
       <c r="K6" t="n">
-        <v>15.53670984496515</v>
+        <v>13.98129662024197</v>
       </c>
       <c r="L6" t="n">
-        <v>42.77747400861591</v>
+        <v>43.58072133981904</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87299523222757</v>
+        <v>99.83822876614617</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.700425596755</v>
+        <v>84.47546683365707</v>
       </c>
       <c r="C7" t="n">
-        <v>40.38851504399129</v>
+        <v>41.48794774415576</v>
       </c>
       <c r="D7" t="n">
-        <v>1.969087078113076</v>
+        <v>1.993222020071834</v>
       </c>
       <c r="E7" t="n">
-        <v>7.709481119593386</v>
+        <v>8.298239167248294</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478678808666129</v>
+        <v>0.7437835438258624</v>
       </c>
       <c r="G7" t="n">
-        <v>30.01391114077061</v>
+        <v>30.51914213060199</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40192251986419</v>
+        <v>34.21404301598967</v>
       </c>
       <c r="I7" t="n">
-        <v>3.183981602130801</v>
+        <v>4.058389807007782</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674174255416331</v>
+        <v>4.648647148911641</v>
       </c>
       <c r="K7" t="n">
-        <v>17.29957440324499</v>
+        <v>15.52453316634293</v>
       </c>
       <c r="L7" t="n">
-        <v>42.20591386242872</v>
+        <v>42.85245572078186</v>
       </c>
       <c r="M7" t="n">
-        <v>99.894003309665</v>
+        <v>99.86493663128056</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.54500865174057</v>
+        <v>82.78295967318995</v>
       </c>
       <c r="C8" t="n">
-        <v>42.69293899231418</v>
+        <v>40.42554495225417</v>
       </c>
       <c r="D8" t="n">
-        <v>1.973286816872502</v>
+        <v>1.913163965417911</v>
       </c>
       <c r="E8" t="n">
-        <v>9.542053460567756</v>
+        <v>8.529373066226043</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494629600081687</v>
+        <v>0.7447978024169567</v>
       </c>
       <c r="G8" t="n">
-        <v>30.51919276937404</v>
+        <v>29.29333631264573</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47529616037576</v>
+        <v>34.26069891118</v>
       </c>
       <c r="I8" t="n">
-        <v>5.601572984491291</v>
+        <v>3.386603350197332</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684143500051054</v>
+        <v>4.65498626510598</v>
       </c>
       <c r="K8" t="n">
-        <v>12.45499134825943</v>
+        <v>17.21704032681004</v>
       </c>
       <c r="L8" t="n">
-        <v>44.6657479534862</v>
+        <v>42.24468167074113</v>
       </c>
       <c r="M8" t="n">
-        <v>99.8136782940598</v>
+        <v>99.88726694980534</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.39766747623608</v>
+        <v>80.93875737113528</v>
       </c>
       <c r="C9" t="n">
-        <v>41.41465107916401</v>
+        <v>39.10683042106827</v>
       </c>
       <c r="D9" t="n">
-        <v>1.875899120076067</v>
+        <v>1.826493987454176</v>
       </c>
       <c r="E9" t="n">
-        <v>9.850540532828614</v>
+        <v>8.613885089745416</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508310154364707</v>
+        <v>0.7456644624038542</v>
       </c>
       <c r="G9" t="n">
-        <v>29.01297792696891</v>
+        <v>27.96629228579113</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53822671007764</v>
+        <v>34.30056527057729</v>
       </c>
       <c r="I9" t="n">
-        <v>4.676498324370445</v>
+        <v>2.825453385139326</v>
       </c>
       <c r="J9" t="n">
-        <v>4.69269384647794</v>
+        <v>4.660402890024089</v>
       </c>
       <c r="K9" t="n">
-        <v>14.6023325237639</v>
+        <v>19.0612426288647</v>
       </c>
       <c r="L9" t="n">
-        <v>43.82741714750289</v>
+        <v>41.73785463478376</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84440075043081</v>
+        <v>99.90592768471674</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.07298954605106</v>
+        <v>85.78784716919556</v>
       </c>
       <c r="C10" t="n">
-        <v>39.81508432128756</v>
+        <v>42.48331304166016</v>
       </c>
       <c r="D10" t="n">
-        <v>1.771626645687846</v>
+        <v>1.828496829500322</v>
       </c>
       <c r="E10" t="n">
-        <v>9.953525875243681</v>
+        <v>10.52582221254015</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520069422477919</v>
+        <v>0.7464821207963138</v>
       </c>
       <c r="G10" t="n">
-        <v>27.40028193205144</v>
+        <v>29.42909695723253</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59231934339842</v>
+        <v>35.7703157892828</v>
       </c>
       <c r="I10" t="n">
-        <v>3.903185418373167</v>
+        <v>2.822120004866471</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700043389048698</v>
+        <v>4.665513254976962</v>
       </c>
       <c r="K10" t="n">
-        <v>16.92701045394896</v>
+        <v>14.21215283080444</v>
       </c>
       <c r="L10" t="n">
-        <v>43.12800249353096</v>
+        <v>43.21056650091078</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87009726876748</v>
+        <v>99.90603237337538</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.64662475412094</v>
+        <v>85.54607216207071</v>
       </c>
       <c r="C11" t="n">
-        <v>37.99318568918584</v>
+        <v>42.56592387460469</v>
       </c>
       <c r="D11" t="n">
-        <v>1.663996261922268</v>
+        <v>1.810415024396956</v>
       </c>
       <c r="E11" t="n">
-        <v>9.891665221526383</v>
+        <v>10.86805019012821</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530193060234286</v>
+        <v>0.7471870558193714</v>
       </c>
       <c r="G11" t="n">
-        <v>25.73565193407198</v>
+        <v>29.18046842839306</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63888807707771</v>
+        <v>35.84648782111606</v>
       </c>
       <c r="I11" t="n">
-        <v>3.257033290852751</v>
+        <v>2.423544543345973</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706370662646427</v>
+        <v>4.669919098871071</v>
       </c>
       <c r="K11" t="n">
-        <v>19.35337524587905</v>
+        <v>14.4539278379293</v>
       </c>
       <c r="L11" t="n">
-        <v>42.5450172477581</v>
+        <v>42.89943968594197</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89157818282298</v>
+        <v>99.91929139847596</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.19643928069601</v>
+        <v>83.64500609009013</v>
       </c>
       <c r="C12" t="n">
-        <v>36.04651298495979</v>
+        <v>41.04165803555509</v>
       </c>
       <c r="D12" t="n">
-        <v>1.556466013175444</v>
+        <v>1.7295852195296</v>
       </c>
       <c r="E12" t="n">
-        <v>9.705338836491459</v>
+        <v>10.71969765925761</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538915572702418</v>
+        <v>0.747788904766898</v>
       </c>
       <c r="G12" t="n">
-        <v>24.07257064148808</v>
+        <v>27.87764474585611</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67901163443112</v>
+        <v>35.87536167646411</v>
       </c>
       <c r="I12" t="n">
-        <v>2.717338364900661</v>
+        <v>2.021247229422685</v>
       </c>
       <c r="J12" t="n">
-        <v>4.71182223293901</v>
+        <v>4.673680654793112</v>
       </c>
       <c r="K12" t="n">
-        <v>21.80356071930398</v>
+        <v>16.35499390990987</v>
       </c>
       <c r="L12" t="n">
-        <v>42.05945314876809</v>
+        <v>42.53602737277544</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90952685303188</v>
+        <v>99.93267931824039</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.8763899929348</v>
+        <v>84.82065878340273</v>
       </c>
       <c r="C13" t="n">
-        <v>34.14562586690023</v>
+        <v>42.02825828419508</v>
       </c>
       <c r="D13" t="n">
-        <v>1.455716853613921</v>
+        <v>1.730850095834301</v>
       </c>
       <c r="E13" t="n">
-        <v>9.454901699590266</v>
+        <v>11.35973383758494</v>
       </c>
       <c r="F13" t="n">
-        <v>0.754642273300033</v>
+        <v>0.748335776037465</v>
       </c>
       <c r="G13" t="n">
-        <v>22.51436683871612</v>
+        <v>28.2200745844078</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71354457180151</v>
+        <v>36.22364038705923</v>
       </c>
       <c r="I13" t="n">
-        <v>2.266703547787753</v>
+        <v>1.860925502244844</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716514208125205</v>
+        <v>4.677098600234157</v>
       </c>
       <c r="K13" t="n">
-        <v>24.12361000706518</v>
+        <v>15.17934121659727</v>
       </c>
       <c r="L13" t="n">
-        <v>41.65528250478735</v>
+        <v>42.7304149802407</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92451837875277</v>
+        <v>99.93801448103306</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.02754568898116</v>
+        <v>82.85285350248746</v>
       </c>
       <c r="C14" t="n">
-        <v>38.62530524965218</v>
+        <v>40.34965088826101</v>
       </c>
       <c r="D14" t="n">
-        <v>1.457410191578917</v>
+        <v>1.649431311805447</v>
       </c>
       <c r="E14" t="n">
-        <v>11.93277538993026</v>
+        <v>11.08399784434405</v>
       </c>
       <c r="F14" t="n">
-        <v>0.755520098138151</v>
+        <v>0.7488029585392657</v>
       </c>
       <c r="G14" t="n">
-        <v>24.52452980188779</v>
+        <v>26.89260887065485</v>
       </c>
       <c r="H14" t="n">
-        <v>36.73789802177415</v>
+        <v>36.24625463521126</v>
       </c>
       <c r="I14" t="n">
-        <v>2.897411572308443</v>
+        <v>1.551739391062185</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722000613363443</v>
+        <v>4.680018490870411</v>
       </c>
       <c r="K14" t="n">
-        <v>16.97245431101886</v>
+        <v>17.14714649751254</v>
       </c>
       <c r="L14" t="n">
-        <v>44.30577226855048</v>
+        <v>42.45151023916409</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90353182922152</v>
+        <v>99.94830762493764</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.33857478509481</v>
+        <v>81.93201342581213</v>
       </c>
       <c r="C15" t="n">
-        <v>38.38368285158052</v>
+        <v>39.63532408704523</v>
       </c>
       <c r="D15" t="n">
-        <v>1.432326781235835</v>
+        <v>1.610317263058133</v>
       </c>
       <c r="E15" t="n">
-        <v>12.13021303016755</v>
+        <v>11.04230991702487</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562593204800158</v>
+        <v>0.7492071983742933</v>
       </c>
       <c r="G15" t="n">
-        <v>24.10243940616643</v>
+        <v>26.25488676196159</v>
       </c>
       <c r="H15" t="n">
-        <v>36.77384342557978</v>
+        <v>36.26582210596844</v>
       </c>
       <c r="I15" t="n">
-        <v>2.416872068465086</v>
+        <v>1.32692518958547</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726620753000098</v>
+        <v>4.682544989839333</v>
       </c>
       <c r="K15" t="n">
-        <v>17.66142521490519</v>
+        <v>18.06798657418787</v>
       </c>
       <c r="L15" t="n">
-        <v>43.87440827872796</v>
+        <v>42.25248236416414</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91951634521368</v>
+        <v>99.95579302539724</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.90023746448814</v>
+        <v>79.44337135283986</v>
       </c>
       <c r="C16" t="n">
-        <v>36.31857789361887</v>
+        <v>37.35237423266681</v>
       </c>
       <c r="D16" t="n">
-        <v>1.340728031176588</v>
+        <v>1.50801617697973</v>
       </c>
       <c r="E16" t="n">
-        <v>11.6904325688488</v>
+        <v>10.52518892880352</v>
       </c>
       <c r="F16" t="n">
-        <v>0.756895293799992</v>
+        <v>0.7495549664864413</v>
       </c>
       <c r="G16" t="n">
-        <v>22.56106396593435</v>
+        <v>24.58695244104809</v>
       </c>
       <c r="H16" t="n">
-        <v>36.80476824549051</v>
+        <v>36.28265602923647</v>
       </c>
       <c r="I16" t="n">
-        <v>2.015753772987951</v>
+        <v>1.106284269745344</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730595586249949</v>
+        <v>4.684718540540258</v>
       </c>
       <c r="K16" t="n">
-        <v>20.09976253551186</v>
+        <v>20.55662864716016</v>
       </c>
       <c r="L16" t="n">
-        <v>43.51452423563412</v>
+        <v>42.054138087129</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93286466476484</v>
+        <v>99.96314096695596</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.74970287713352</v>
+        <v>84.01179684987378</v>
       </c>
       <c r="C17" t="n">
-        <v>37.65674779698418</v>
+        <v>40.40627751170503</v>
       </c>
       <c r="D17" t="n">
-        <v>1.341824460902093</v>
+        <v>1.50872182585238</v>
       </c>
       <c r="E17" t="n">
-        <v>12.52147607546674</v>
+        <v>12.147386451436</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575142728023841</v>
+        <v>0.749905707164933</v>
       </c>
       <c r="G17" t="n">
-        <v>23.06672818019379</v>
+        <v>26.01917091339874</v>
       </c>
       <c r="H17" t="n">
-        <v>37.32208077350953</v>
+        <v>37.72034729437133</v>
       </c>
       <c r="I17" t="n">
-        <v>2.005614909244085</v>
+        <v>1.179353987869562</v>
       </c>
       <c r="J17" t="n">
-        <v>4.7344642050149</v>
+        <v>4.686910669780831</v>
       </c>
       <c r="K17" t="n">
-        <v>18.25029712286651</v>
+        <v>15.98820315012622</v>
       </c>
       <c r="L17" t="n">
-        <v>44.02615587734943</v>
+        <v>43.56622592521443</v>
       </c>
       <c r="M17" t="n">
-        <v>99.9332007972001</v>
+        <v>99.96070658704568</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.42634784764819</v>
+        <v>85.48439877128992</v>
       </c>
       <c r="C18" t="n">
-        <v>35.64274558616361</v>
+        <v>41.07585886113179</v>
       </c>
       <c r="D18" t="n">
-        <v>1.258289720058707</v>
+        <v>1.509862067754501</v>
       </c>
       <c r="E18" t="n">
-        <v>12.0207097809067</v>
+        <v>12.69835464471379</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580459842450159</v>
+        <v>0.7504724610192866</v>
       </c>
       <c r="G18" t="n">
-        <v>21.63071831692009</v>
+        <v>26.14821345902507</v>
       </c>
       <c r="H18" t="n">
-        <v>37.34827774183422</v>
+        <v>37.7488550814336</v>
       </c>
       <c r="I18" t="n">
-        <v>1.672518902152126</v>
+        <v>1.938188175973118</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737787401531349</v>
+        <v>4.690452881370541</v>
       </c>
       <c r="K18" t="n">
-        <v>20.5736521523518</v>
+        <v>14.51560122871009</v>
       </c>
       <c r="L18" t="n">
-        <v>43.72789073622783</v>
+        <v>44.34398242802889</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94428847474325</v>
+        <v>99.93544251787077</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.5521604218787</v>
+        <v>82.73170583578339</v>
       </c>
       <c r="C19" t="n">
-        <v>35.02251445471651</v>
+        <v>38.62340249922463</v>
       </c>
       <c r="D19" t="n">
-        <v>1.227367534136087</v>
+        <v>1.407791228697836</v>
       </c>
       <c r="E19" t="n">
-        <v>11.95827727838219</v>
+        <v>12.10927895287966</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7584956340007701</v>
+        <v>0.7509611571877466</v>
       </c>
       <c r="G19" t="n">
-        <v>21.09914829550688</v>
+        <v>24.38052212840914</v>
       </c>
       <c r="H19" t="n">
-        <v>37.37043160098457</v>
+        <v>37.77343655750401</v>
       </c>
       <c r="I19" t="n">
-        <v>1.397842366363381</v>
+        <v>1.616208578681583</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740597712504813</v>
+        <v>4.693507232423416</v>
       </c>
       <c r="K19" t="n">
-        <v>21.44783957812133</v>
+        <v>17.26829416421659</v>
       </c>
       <c r="L19" t="n">
-        <v>43.48307884381389</v>
+        <v>44.05446477611507</v>
       </c>
       <c r="M19" t="n">
-        <v>99.9534328766517</v>
+        <v>99.94616143955631</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.01772963598033</v>
+        <v>79.85625516733789</v>
       </c>
       <c r="C20" t="n">
-        <v>32.7030027292336</v>
+        <v>35.99757621243462</v>
       </c>
       <c r="D20" t="n">
-        <v>1.137217863608562</v>
+        <v>1.301707963994363</v>
       </c>
       <c r="E20" t="n">
-        <v>11.27419042944118</v>
+        <v>11.42139117365917</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7588832625698712</v>
+        <v>0.7513835802951612</v>
       </c>
       <c r="G20" t="n">
-        <v>19.54942401622638</v>
+        <v>22.5433424885351</v>
       </c>
       <c r="H20" t="n">
-        <v>37.38952972927804</v>
+        <v>37.79468449063028</v>
       </c>
       <c r="I20" t="n">
-        <v>1.165463943794604</v>
+        <v>1.347598093379053</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743020391061694</v>
+        <v>4.696147376844757</v>
       </c>
       <c r="K20" t="n">
-        <v>23.98227036401968</v>
+        <v>20.14374483266212</v>
       </c>
       <c r="L20" t="n">
-        <v>43.27589795212554</v>
+        <v>43.81378427216208</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96117104537882</v>
+        <v>99.95510531725881</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.84435317329992</v>
+        <v>77.0370782772998</v>
       </c>
       <c r="C21" t="n">
-        <v>36.36039246428422</v>
+        <v>33.3858147183039</v>
       </c>
       <c r="D21" t="n">
-        <v>1.137964812534589</v>
+        <v>1.198232494292135</v>
       </c>
       <c r="E21" t="n">
-        <v>13.23752242926561</v>
+        <v>10.70073845963154</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7593817132679259</v>
+        <v>0.7517488644757435</v>
       </c>
       <c r="G21" t="n">
-        <v>21.24940578979769</v>
+        <v>20.75132537165322</v>
       </c>
       <c r="H21" t="n">
-        <v>39.10122926444014</v>
+        <v>37.81305832886228</v>
       </c>
       <c r="I21" t="n">
-        <v>1.612713456069441</v>
+        <v>1.123544355411462</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746135707924537</v>
+        <v>4.698430402973397</v>
       </c>
       <c r="K21" t="n">
-        <v>18.15564682670007</v>
+        <v>22.96292172270022</v>
       </c>
       <c r="L21" t="n">
-        <v>45.43023887945582</v>
+        <v>43.61383027862425</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94627817044011</v>
+        <v>99.96256671962836</v>
       </c>
     </row>
   </sheetData>
